--- a/event_planner_forms/005_secret_santa_favorites_form--event_planner_forms.xlsx
+++ b/event_planner_forms/005_secret_santa_favorites_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1449,17 +1449,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>favorite_book_choices</t>
+          <t>favorite_game_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>the_hitchhiker's_guide_to_the_galaxy</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Hitchhiker's Guide to the Galaxy</t>
+          <t>Football</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Baseball</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>baseball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baseball</t>
+          <t>Hockey</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>favorite_game_choices</t>
+          <t>favorite_song_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>imagine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Imagine</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>imagine</t>
+          <t>i_want_it_that_way</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Imagine</t>
+          <t>I Want It That Way</t>
         </is>
       </c>
     </row>
@@ -1556,46 +1556,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>imagine</t>
+          <t>i_will_always_love_you</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Imagine</t>
+          <t>I Will Always Love You</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>favorite_song_choices</t>
+          <t>favorite_band_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>i_want_it_that_way</t>
+          <t>the_beatles</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>I Want It That Way</t>
+          <t>The Beatles</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>favorite_song_choices</t>
+          <t>favorite_band_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>i_will_always_love_you</t>
+          <t>the_rolling_stones</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>I Will Always Love You</t>
+          <t>The Rolling Stones</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>the_beatles</t>
+          <t>queen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Beatles</t>
+          <t>Queen</t>
         </is>
       </c>
     </row>
@@ -1624,46 +1624,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>the_rolling_stones</t>
+          <t>the_who</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Rolling Stones</t>
+          <t>The Who</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>favorite_band_choices</t>
+          <t>favorite_drink_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>queen</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Queen</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>favorite_band_choices</t>
+          <t>favorite_drink_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>the_who</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Who</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>rosé</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Rosé</t>
         </is>
       </c>
     </row>
@@ -1692,46 +1692,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>sparkling</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Sparkling</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>favorite_drink_type_choices</t>
+          <t>favorite_coffee_cup_size_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>rosé</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>favorite_drink_type_choices</t>
+          <t>favorite_coffee_cup_size_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sparkling</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Tall</t>
         </is>
       </c>
     </row>
@@ -1760,46 +1760,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>grande</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Grande</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>favorite_coffee_cup_size_choices</t>
+          <t>favorite_soda_size_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>favorite_coffee_cup_size_choices</t>
+          <t>favorite_soda_size_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>grande</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Grande</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1828,46 +1828,46 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>favorite_soda_size_choices</t>
+          <t>favorite_dessert_type_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>favorite_soda_size_choices</t>
+          <t>favorite_dessert_type_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>extra_large</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Extra Large</t>
+          <t>Chocolate</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>caramel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Caramel</t>
         </is>
       </c>
     </row>
@@ -1896,46 +1896,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>favorite_dessert_type_choices</t>
+          <t>favorite_dessert_topping_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>caramel</t>
+          <t>sprinkles</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Sprinkles</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>favorite_dessert_type_choices</t>
+          <t>favorite_dessert_topping_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>whipped_cream</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Whipped cream</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>sprinkles</t>
+          <t>nuts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sprinkles</t>
+          <t>Nuts</t>
         </is>
       </c>
     </row>
@@ -1964,46 +1964,46 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>whipped_cream</t>
+          <t>chocolate_chips</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Whipped cream</t>
+          <t>Chocolate chips</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>favorite_dessert_topping_choices</t>
+          <t>favorite_dessert_flavor_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nuts</t>
+          <t>vanilla</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nuts</t>
+          <t>Vanilla</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>favorite_dessert_topping_choices</t>
+          <t>favorite_dessert_flavor_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>chocolate_chips</t>
+          <t>chocolate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chocolate chips</t>
+          <t>Chocolate</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>vanilla</t>
+          <t>strawberry</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vanilla</t>
+          <t>Strawberry</t>
         </is>
       </c>
     </row>
@@ -2032,46 +2032,46 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>chocolate</t>
+          <t>caramel</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chocolate</t>
+          <t>Caramel</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>favorite_dessert_flavor_choices</t>
+          <t>favorite_pizza_topping_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>strawberry</t>
+          <t>pepperoni</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Strawberry</t>
+          <t>Pepperoni</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>favorite_dessert_flavor_choices</t>
+          <t>favorite_pizza_topping_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>caramel</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Mushrooms</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pepperoni</t>
+          <t>sausage</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pepperoni</t>
+          <t>Sausage</t>
         </is>
       </c>
     </row>
@@ -2100,44 +2100,10 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olives</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
-        <is>
-          <t>Mushrooms</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>favorite_pizza_topping_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>sausage</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Sausage</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>favorite_pizza_topping_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>olives</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
         <is>
           <t>Olives</t>
         </is>
